--- a/test_files/evidence_table.xlsx
+++ b/test_files/evidence_table.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
   <si>
     <t>Label</t>
   </si>
@@ -24,6 +24,9 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Tags</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
@@ -40,6 +43,9 @@
   </si>
   <si>
     <t>constant</t>
+  </si>
+  <si>
+    <t>VOI</t>
   </si>
   <si>
     <t>From</t>
@@ -415,39 +421,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -462,46 +480,46 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -516,44 +534,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
